--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/41.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/41.xlsx
@@ -426,13 +426,13 @@
         <v>-20.78267455667371</v>
       </c>
       <c r="E2">
-        <v>-19.33004080479889</v>
+        <v>-9.941212372876315</v>
       </c>
       <c r="F2">
-        <v>-0.6428820063143564</v>
+        <v>1.039031854860148</v>
       </c>
       <c r="G2">
-        <v>-16.78288779401454</v>
+        <v>-13.26838958002934</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.62117851576564</v>
       </c>
       <c r="E3">
-        <v>-19.28203798830652</v>
+        <v>-10.40339834194853</v>
       </c>
       <c r="F3">
-        <v>-0.471752069672215</v>
+        <v>1.165579886251023</v>
       </c>
       <c r="G3">
-        <v>-16.25966063827575</v>
+        <v>-13.06854882993028</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.17977550273997</v>
       </c>
       <c r="E4">
-        <v>-20.3979311134841</v>
+        <v>-10.63128504734188</v>
       </c>
       <c r="F4">
-        <v>-0.7508423015538133</v>
+        <v>1.084606972627372</v>
       </c>
       <c r="G4">
-        <v>-16.07248199944359</v>
+        <v>-12.6328351382579</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.45599600378197</v>
       </c>
       <c r="E5">
-        <v>-21.00606923493345</v>
+        <v>-11.1074050404089</v>
       </c>
       <c r="F5">
-        <v>-1.293851216334737</v>
+        <v>1.188487558408041</v>
       </c>
       <c r="G5">
-        <v>-16.19267154281238</v>
+        <v>-13.02044586083902</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.46609831300704</v>
       </c>
       <c r="E6">
-        <v>-23.1231520949195</v>
+        <v>-11.61006820705289</v>
       </c>
       <c r="F6">
-        <v>-0.6296885986899687</v>
+        <v>1.422980146057719</v>
       </c>
       <c r="G6">
-        <v>-15.50607573891238</v>
+        <v>-12.128974485896</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.24335711464511</v>
       </c>
       <c r="E7">
-        <v>-19.94518539375322</v>
+        <v>-12.97776222843218</v>
       </c>
       <c r="F7">
-        <v>-0.3071736908188148</v>
+        <v>1.471293846458598</v>
       </c>
       <c r="G7">
-        <v>-15.41997338229746</v>
+        <v>-11.55158351749768</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.83287802908305</v>
       </c>
       <c r="E8">
-        <v>-22.38385971304339</v>
+        <v>-13.27790650445489</v>
       </c>
       <c r="F8">
-        <v>-0.4565937745683868</v>
+        <v>1.729698087557487</v>
       </c>
       <c r="G8">
-        <v>-15.60847958475421</v>
+        <v>-10.6568095506469</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.27647741252285</v>
       </c>
       <c r="E9">
-        <v>-22.99730979177719</v>
+        <v>-13.58092480271438</v>
       </c>
       <c r="F9">
-        <v>-0.616474481880511</v>
+        <v>1.66995126026317</v>
       </c>
       <c r="G9">
-        <v>-15.21962092625854</v>
+        <v>-10.58646434301165</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.63016493513795</v>
       </c>
       <c r="E10">
-        <v>-23.26367184688375</v>
+        <v>-14.86999022729201</v>
       </c>
       <c r="F10">
-        <v>-0.1053842198642581</v>
+        <v>1.769416647786917</v>
       </c>
       <c r="G10">
-        <v>-13.82044066142631</v>
+        <v>-10.32995477081788</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.92647449674868</v>
       </c>
       <c r="E11">
-        <v>-23.5711008555702</v>
+        <v>-16.38779376558458</v>
       </c>
       <c r="F11">
-        <v>-0.6860540302460583</v>
+        <v>2.010602444051216</v>
       </c>
       <c r="G11">
-        <v>-13.94323311715244</v>
+        <v>-9.882439208221378</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.22494631347795</v>
       </c>
       <c r="E12">
-        <v>-23.62531687620451</v>
+        <v>-16.33572080199388</v>
       </c>
       <c r="F12">
-        <v>-0.1353686347433918</v>
+        <v>2.199857887834013</v>
       </c>
       <c r="G12">
-        <v>-12.98699177964849</v>
+        <v>-8.955888563579864</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-7.552815308803468</v>
       </c>
       <c r="E13">
-        <v>-24.701214576324</v>
+        <v>-17.02566057369705</v>
       </c>
       <c r="F13">
-        <v>-0.2444414274048083</v>
+        <v>2.059759422468144</v>
       </c>
       <c r="G13">
-        <v>-12.2753341330461</v>
+        <v>-9.278479997491594</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.974768769868301</v>
       </c>
       <c r="E14">
-        <v>-25.92124116904901</v>
+        <v>-17.73470927070575</v>
       </c>
       <c r="F14">
-        <v>0.1087048502870658</v>
+        <v>2.527101116840347</v>
       </c>
       <c r="G14">
-        <v>-13.56801298840075</v>
+        <v>-8.633412002430141</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.515268164251353</v>
       </c>
       <c r="E15">
-        <v>-25.97115030953947</v>
+        <v>-18.64337376361969</v>
       </c>
       <c r="F15">
-        <v>0.2211143068469587</v>
+        <v>2.479322541781677</v>
       </c>
       <c r="G15">
-        <v>-12.35774359143689</v>
+        <v>-8.276393984967696</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.224170656427305</v>
       </c>
       <c r="E16">
-        <v>-25.62561143373639</v>
+        <v>-18.87259780305962</v>
       </c>
       <c r="F16">
-        <v>0.2701006415789102</v>
+        <v>2.946336202662371</v>
       </c>
       <c r="G16">
-        <v>-11.81779331121973</v>
+        <v>-7.214229517913098</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.108160321269795</v>
       </c>
       <c r="E17">
-        <v>-27.50743563822752</v>
+        <v>-19.8917709429046</v>
       </c>
       <c r="F17">
-        <v>0.4569521631587835</v>
+        <v>2.953877659497458</v>
       </c>
       <c r="G17">
-        <v>-10.68173694000285</v>
+        <v>-6.812984181704897</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.187304870828552</v>
       </c>
       <c r="E18">
-        <v>-28.2682437313719</v>
+        <v>-20.95956988094067</v>
       </c>
       <c r="F18">
-        <v>0.537934188823866</v>
+        <v>3.278987014074179</v>
       </c>
       <c r="G18">
-        <v>-10.21018294658367</v>
+        <v>-6.058445055193473</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.4466947000705115</v>
       </c>
       <c r="E19">
-        <v>-28.5021442867636</v>
+        <v>-21.79930767870775</v>
       </c>
       <c r="F19">
-        <v>0.8078013780426946</v>
+        <v>3.490961262246156</v>
       </c>
       <c r="G19">
-        <v>-9.211494818145106</v>
+        <v>-6.166511606053425</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.119754371949893</v>
       </c>
       <c r="E20">
-        <v>-29.82402838723003</v>
+        <v>-22.47386395566375</v>
       </c>
       <c r="F20">
-        <v>1.400244774320484</v>
+        <v>3.89638083652429</v>
       </c>
       <c r="G20">
-        <v>-9.044044270815691</v>
+        <v>-5.161489811236819</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.53863927007166</v>
       </c>
       <c r="E21">
-        <v>-29.59814145308959</v>
+        <v>-23.40148370506421</v>
       </c>
       <c r="F21">
-        <v>1.321536617176086</v>
+        <v>3.680930758730167</v>
       </c>
       <c r="G21">
-        <v>-9.247340341381092</v>
+        <v>-5.229789500484934</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8282172740649797</v>
       </c>
       <c r="E22">
-        <v>-30.24113955379388</v>
+        <v>-23.80778821576086</v>
       </c>
       <c r="F22">
-        <v>1.72818714541478</v>
+        <v>3.658110893517846</v>
       </c>
       <c r="G22">
-        <v>-8.780139764567595</v>
+        <v>-4.942025399418654</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.012872756495056</v>
       </c>
       <c r="E23">
-        <v>-30.38679267495562</v>
+        <v>-23.22932063601609</v>
       </c>
       <c r="F23">
-        <v>1.761560411338767</v>
+        <v>3.788204337392703</v>
       </c>
       <c r="G23">
-        <v>-8.717459703051851</v>
+        <v>-4.950042996057963</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.109546442345256</v>
       </c>
       <c r="E24">
-        <v>-32.39142733832193</v>
+        <v>-24.07449083419605</v>
       </c>
       <c r="F24">
-        <v>1.174779734626515</v>
+        <v>4.200872126445333</v>
       </c>
       <c r="G24">
-        <v>-9.623792741579784</v>
+        <v>-4.880900036306919</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.133123077557782</v>
       </c>
       <c r="E25">
-        <v>-32.19682862169709</v>
+        <v>-24.20005902539091</v>
       </c>
       <c r="F25">
-        <v>1.761971281570555</v>
+        <v>4.040475346241265</v>
       </c>
       <c r="G25">
-        <v>-9.031356052102881</v>
+        <v>-4.966367981986195</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.094586383001813</v>
       </c>
       <c r="E26">
-        <v>-31.17711141116856</v>
+        <v>-24.271801597816</v>
       </c>
       <c r="F26">
-        <v>1.79561625200266</v>
+        <v>4.020442108971961</v>
       </c>
       <c r="G26">
-        <v>-9.532453231315095</v>
+        <v>-4.914865823437302</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.002134885542246</v>
       </c>
       <c r="E27">
-        <v>-30.16198349915397</v>
+        <v>-24.43122261451954</v>
       </c>
       <c r="F27">
-        <v>1.864826348506559</v>
+        <v>4.025022980709442</v>
       </c>
       <c r="G27">
-        <v>-9.718810790973352</v>
+        <v>-4.997174768161331</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.8659249175762326</v>
       </c>
       <c r="E28">
-        <v>-30.49452697672167</v>
+        <v>-24.43890605547048</v>
       </c>
       <c r="F28">
-        <v>1.376770498859952</v>
+        <v>3.837823544820393</v>
       </c>
       <c r="G28">
-        <v>-8.73546339775217</v>
+        <v>-5.038599452588525</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.6967443784089065</v>
       </c>
       <c r="E29">
-        <v>-31.40227568653848</v>
+        <v>-24.43731122232174</v>
       </c>
       <c r="F29">
-        <v>2.021463997436723</v>
+        <v>4.086514349754055</v>
       </c>
       <c r="G29">
-        <v>-8.755512610839624</v>
+        <v>-5.287014411177545</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.5050521519239483</v>
       </c>
       <c r="E30">
-        <v>-30.05439455978429</v>
+        <v>-24.05482122536166</v>
       </c>
       <c r="F30">
-        <v>1.659021780750633</v>
+        <v>3.949974550750613</v>
       </c>
       <c r="G30">
-        <v>-9.629230922563075</v>
+        <v>-5.056775456431856</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.3044914963222018</v>
       </c>
       <c r="E31">
-        <v>-29.86235214472988</v>
+        <v>-23.95327105525828</v>
       </c>
       <c r="F31">
-        <v>1.926117252639694</v>
+        <v>4.006573581914292</v>
       </c>
       <c r="G31">
-        <v>-10.16278618390431</v>
+        <v>-5.40857067933978</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.1059664817346284</v>
       </c>
       <c r="E32">
-        <v>-30.22531374204062</v>
+        <v>-23.726165153594</v>
       </c>
       <c r="F32">
-        <v>1.452431920696853</v>
+        <v>3.962840753250895</v>
       </c>
       <c r="G32">
-        <v>-9.387838866924149</v>
+        <v>-5.454300481597721</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-0.07980961416508051</v>
       </c>
       <c r="E33">
-        <v>-29.57913635806717</v>
+        <v>-24.09690571571615</v>
       </c>
       <c r="F33">
-        <v>1.376386136385053</v>
+        <v>4.022029260915725</v>
       </c>
       <c r="G33">
-        <v>-9.044555976755548</v>
+        <v>-5.797490690333335</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-0.2513525453637637</v>
       </c>
       <c r="E34">
-        <v>-30.04279671715971</v>
+        <v>-22.88286805372154</v>
       </c>
       <c r="F34">
-        <v>2.528257517734655</v>
+        <v>4.131065605411418</v>
       </c>
       <c r="G34">
-        <v>-9.442355130103481</v>
+        <v>-5.285784750475131</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.4086928201307147</v>
       </c>
       <c r="E35">
-        <v>-28.90135095930611</v>
+        <v>-23.41722437598531</v>
       </c>
       <c r="F35">
-        <v>2.110646032022118</v>
+        <v>4.405331425539112</v>
       </c>
       <c r="G35">
-        <v>-9.748852628983293</v>
+        <v>-5.423966240193575</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.5610110406151222</v>
       </c>
       <c r="E36">
-        <v>-29.07170738142793</v>
+        <v>-22.28539537895436</v>
       </c>
       <c r="F36">
-        <v>2.246034400335669</v>
+        <v>4.059199763014145</v>
       </c>
       <c r="G36">
-        <v>-10.16270655619428</v>
+        <v>-5.774821595048699</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.7143861796625136</v>
       </c>
       <c r="E37">
-        <v>-30.35511197896982</v>
+        <v>-21.76494816141744</v>
       </c>
       <c r="F37">
-        <v>2.182331290325581</v>
+        <v>4.269540470667801</v>
       </c>
       <c r="G37">
-        <v>-9.463003509074595</v>
+        <v>-5.206543430645661</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-0.8789179619788682</v>
       </c>
       <c r="E38">
-        <v>-28.18533317369435</v>
+        <v>-22.16945433161044</v>
       </c>
       <c r="F38">
-        <v>1.825351328293551</v>
+        <v>4.423807332091153</v>
       </c>
       <c r="G38">
-        <v>-10.5204947433111</v>
+        <v>-5.611710105229714</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-1.060100864069762</v>
       </c>
       <c r="E39">
-        <v>-27.92734606922431</v>
+        <v>-21.26250926818498</v>
       </c>
       <c r="F39">
-        <v>2.429618840878901</v>
+        <v>4.218599188865242</v>
       </c>
       <c r="G39">
-        <v>-10.78546573872467</v>
+        <v>-5.664368823632469</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.263347720299369</v>
       </c>
       <c r="E40">
-        <v>-26.89347471450077</v>
+        <v>-20.86672899498545</v>
       </c>
       <c r="F40">
-        <v>1.274530080536826</v>
+        <v>4.636747456654794</v>
       </c>
       <c r="G40">
-        <v>-9.674566502387757</v>
+        <v>-5.966358871975725</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.489045583163337</v>
       </c>
       <c r="E41">
-        <v>-27.08186853340632</v>
+        <v>-20.41275807791374</v>
       </c>
       <c r="F41">
-        <v>2.087329146368117</v>
+        <v>4.69638162598233</v>
       </c>
       <c r="G41">
-        <v>-10.75844061608976</v>
+        <v>-5.991033019106337</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.733575946527135</v>
       </c>
       <c r="E42">
-        <v>-26.94198006956344</v>
+        <v>-19.92095555888417</v>
       </c>
       <c r="F42">
-        <v>2.157886168268968</v>
+        <v>4.723321790656176</v>
       </c>
       <c r="G42">
-        <v>-9.746589113422798</v>
+        <v>-5.823018550945241</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.988779011354484</v>
       </c>
       <c r="E43">
-        <v>-25.41653877564452</v>
+        <v>-19.31653040835922</v>
       </c>
       <c r="F43">
-        <v>2.571943957823495</v>
+        <v>4.575024144737396</v>
       </c>
       <c r="G43">
-        <v>-10.82603018280909</v>
+        <v>-6.019364819409098</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.241884930826808</v>
       </c>
       <c r="E44">
-        <v>-25.83313909721542</v>
+        <v>-18.56147658950539</v>
       </c>
       <c r="F44">
-        <v>2.320219671460781</v>
+        <v>4.325778333643859</v>
       </c>
       <c r="G44">
-        <v>-10.43330501157399</v>
+        <v>-6.383080702120045</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.482405284926992</v>
       </c>
       <c r="E45">
-        <v>-24.20098103830502</v>
+        <v>-18.86040812782125</v>
       </c>
       <c r="F45">
-        <v>1.447373909335359</v>
+        <v>4.341089876717205</v>
       </c>
       <c r="G45">
-        <v>-11.45011953970865</v>
+        <v>-6.100449324919895</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.699629712975804</v>
       </c>
       <c r="E46">
-        <v>-25.60136498602204</v>
+        <v>-18.32126730611128</v>
       </c>
       <c r="F46">
-        <v>2.463512321531846</v>
+        <v>4.668444106955514</v>
       </c>
       <c r="G46">
-        <v>-10.72367594111449</v>
+        <v>-6.211426855998938</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.889902520721353</v>
       </c>
       <c r="E47">
-        <v>-25.37735738000609</v>
+        <v>-18.13188502291043</v>
       </c>
       <c r="F47">
-        <v>2.080413935289547</v>
+        <v>4.876737090389449</v>
       </c>
       <c r="G47">
-        <v>-11.54485954480326</v>
+        <v>-6.801742315495563</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.049159609802347</v>
       </c>
       <c r="E48">
-        <v>-22.27596343603567</v>
+        <v>-16.87034292978243</v>
       </c>
       <c r="F48">
-        <v>1.990726596588445</v>
+        <v>4.628412423847824</v>
       </c>
       <c r="G48">
-        <v>-11.19640607497197</v>
+        <v>-6.090559824408757</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.181995905562555</v>
       </c>
       <c r="E49">
-        <v>-24.07003443844451</v>
+        <v>-16.87094099221321</v>
       </c>
       <c r="F49">
-        <v>1.627146203090908</v>
+        <v>4.48618174078715</v>
       </c>
       <c r="G49">
-        <v>-11.69314461608932</v>
+        <v>-6.475542832558913</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.290916624507676</v>
       </c>
       <c r="E50">
-        <v>-22.57837536544174</v>
+        <v>-16.52815984872981</v>
       </c>
       <c r="F50">
-        <v>2.066005312685252</v>
+        <v>4.721807535043858</v>
       </c>
       <c r="G50">
-        <v>-10.27819675929906</v>
+        <v>-6.603370109229002</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.388053558982951</v>
       </c>
       <c r="E51">
-        <v>-23.94035872124939</v>
+        <v>-15.38314440574253</v>
       </c>
       <c r="F51">
-        <v>1.796729577792023</v>
+        <v>4.373151008675157</v>
       </c>
       <c r="G51">
-        <v>-10.88348483902572</v>
+        <v>-6.466165037987635</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.481193077402015</v>
       </c>
       <c r="E52">
-        <v>-22.53811413485885</v>
+        <v>-15.46838906818463</v>
       </c>
       <c r="F52">
-        <v>2.216002768514576</v>
+        <v>4.306979363804727</v>
       </c>
       <c r="G52">
-        <v>-10.89150113029273</v>
+        <v>-6.415540089621357</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.586760202471142</v>
       </c>
       <c r="E53">
-        <v>-21.25696888427766</v>
+        <v>-14.32442438766254</v>
       </c>
       <c r="F53">
-        <v>1.57231987816922</v>
+        <v>4.471557742658127</v>
       </c>
       <c r="G53">
-        <v>-10.7236132832443</v>
+        <v>-6.356135207195165</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.713328464067124</v>
       </c>
       <c r="E54">
-        <v>-20.20250175459429</v>
+        <v>-14.13794935238906</v>
       </c>
       <c r="F54">
-        <v>1.610370106449412</v>
+        <v>4.243067505209134</v>
       </c>
       <c r="G54">
-        <v>-10.85053463154128</v>
+        <v>-6.95651247634594</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.874667125096503</v>
       </c>
       <c r="E55">
-        <v>-21.20742107317246</v>
+        <v>-14.11048416589797</v>
       </c>
       <c r="F55">
-        <v>1.867117612742702</v>
+        <v>4.364806035459355</v>
       </c>
       <c r="G55">
-        <v>-11.72795758983952</v>
+        <v>-6.994081091012061</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.075173501175517</v>
       </c>
       <c r="E56">
-        <v>-18.42073671734093</v>
+        <v>-13.50479643913027</v>
       </c>
       <c r="F56">
-        <v>2.025509743831996</v>
+        <v>4.128491039523517</v>
       </c>
       <c r="G56">
-        <v>-12.23915443450245</v>
+        <v>-7.000741100463991</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.319949047577525</v>
       </c>
       <c r="E57">
-        <v>-20.69932550611558</v>
+        <v>-13.22484507656888</v>
       </c>
       <c r="F57">
-        <v>1.901168483202179</v>
+        <v>4.328412541984761</v>
       </c>
       <c r="G57">
-        <v>-11.11695328483061</v>
+        <v>-7.576650471306853</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.606482897933678</v>
       </c>
       <c r="E58">
-        <v>-21.41822146717546</v>
+        <v>-12.81360239760701</v>
       </c>
       <c r="F58">
-        <v>1.38669434034549</v>
+        <v>4.448295529252712</v>
       </c>
       <c r="G58">
-        <v>-11.65323546889726</v>
+        <v>-7.228241384133603</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.930013783719425</v>
       </c>
       <c r="E59">
-        <v>-20.78440819331602</v>
+        <v>-12.85890562673824</v>
       </c>
       <c r="F59">
-        <v>1.730244810043334</v>
+        <v>4.166933913952637</v>
       </c>
       <c r="G59">
-        <v>-12.35366821913016</v>
+        <v>-7.815909548614838</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.282647369959793</v>
       </c>
       <c r="E60">
-        <v>-19.54414300180512</v>
+        <v>-12.5001761517675</v>
       </c>
       <c r="F60">
-        <v>1.863361794938409</v>
+        <v>4.080467267713619</v>
       </c>
       <c r="G60">
-        <v>-12.27378726687587</v>
+        <v>-7.641925612946163</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.653784855796075</v>
       </c>
       <c r="E61">
-        <v>-19.18653074068076</v>
+        <v>-12.51330860597661</v>
       </c>
       <c r="F61">
-        <v>1.873176291926778</v>
+        <v>4.177926349387787</v>
       </c>
       <c r="G61">
-        <v>-12.99032308974675</v>
+        <v>-7.905172211557297</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.03521008115997</v>
       </c>
       <c r="E62">
-        <v>-20.26059272139467</v>
+        <v>-10.955970649083</v>
       </c>
       <c r="F62">
-        <v>2.025572699754608</v>
+        <v>4.145056730844702</v>
       </c>
       <c r="G62">
-        <v>-11.70063223157663</v>
+        <v>-8.49753580018565</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.415569126829348</v>
       </c>
       <c r="E63">
-        <v>-19.12892154639407</v>
+        <v>-12.24178410919329</v>
       </c>
       <c r="F63">
-        <v>1.055887474772313</v>
+        <v>4.13092975315736</v>
       </c>
       <c r="G63">
-        <v>-12.15790414671012</v>
+        <v>-8.493282897246727</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.79001129090971</v>
       </c>
       <c r="E64">
-        <v>-19.32461671080866</v>
+        <v>-11.46488024555954</v>
       </c>
       <c r="F64">
-        <v>1.626564689174143</v>
+        <v>4.180171225049373</v>
       </c>
       <c r="G64">
-        <v>-12.08936687970422</v>
+        <v>-8.37622494201498</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.148899321052278</v>
       </c>
       <c r="E65">
-        <v>-19.34582300783324</v>
+        <v>-10.88950265504044</v>
       </c>
       <c r="F65">
-        <v>1.91459963227117</v>
+        <v>3.872828694527895</v>
       </c>
       <c r="G65">
-        <v>-12.68604733451398</v>
+        <v>-8.61966382141334</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.491069955440598</v>
       </c>
       <c r="E66">
-        <v>-19.0638241120887</v>
+        <v>-11.34906379455537</v>
       </c>
       <c r="F66">
-        <v>1.927906526229741</v>
+        <v>3.761588892740755</v>
       </c>
       <c r="G66">
-        <v>-12.65502646728237</v>
+        <v>-9.209793918043996</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.807917151672394</v>
       </c>
       <c r="E67">
-        <v>-17.99573029604857</v>
+        <v>-11.40552254930509</v>
       </c>
       <c r="F67">
-        <v>1.800079495568944</v>
+        <v>4.161491540116244</v>
       </c>
       <c r="G67">
-        <v>-11.45042499682581</v>
+        <v>-8.945952069666086</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.101293339271411</v>
       </c>
       <c r="E68">
-        <v>-18.28479795746797</v>
+        <v>-10.38263643853572</v>
       </c>
       <c r="F68">
-        <v>1.820583245523037</v>
+        <v>3.858719940923414</v>
       </c>
       <c r="G68">
-        <v>-12.00820927334487</v>
+        <v>-8.830165547050212</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.365126140240379</v>
       </c>
       <c r="E69">
-        <v>-19.93878114189033</v>
+        <v>-11.27042689133107</v>
       </c>
       <c r="F69">
-        <v>1.37343217822667</v>
+        <v>3.746501008866165</v>
       </c>
       <c r="G69">
-        <v>-12.53963677784434</v>
+        <v>-8.554474834345536</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.604580227169169</v>
       </c>
       <c r="E70">
-        <v>-17.78846013167168</v>
+        <v>-11.64495933539278</v>
       </c>
       <c r="F70">
-        <v>1.489703483618414</v>
+        <v>3.82830063315781</v>
       </c>
       <c r="G70">
-        <v>-12.74647823956447</v>
+        <v>-8.669104797107547</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.8162548669473</v>
       </c>
       <c r="E71">
-        <v>-17.81241585459329</v>
+        <v>-10.53695315852105</v>
       </c>
       <c r="F71">
-        <v>1.436583595546493</v>
+        <v>3.834304640093301</v>
       </c>
       <c r="G71">
-        <v>-13.15473081425522</v>
+        <v>-8.605986130500497</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.006496707690491</v>
       </c>
       <c r="E72">
-        <v>-19.53747294441745</v>
+        <v>-11.05209257198483</v>
       </c>
       <c r="F72">
-        <v>1.58233318333426</v>
+        <v>3.971096262787194</v>
       </c>
       <c r="G72">
-        <v>-11.93191548415876</v>
+        <v>-8.572909301903387</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.173450987723555</v>
       </c>
       <c r="E73">
-        <v>-17.50833848744597</v>
+        <v>-11.09402754673162</v>
       </c>
       <c r="F73">
-        <v>1.493189253649394</v>
+        <v>3.743462557232696</v>
       </c>
       <c r="G73">
-        <v>-12.6397118395109</v>
+        <v>-8.231341670931149</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.322079201898688</v>
       </c>
       <c r="E74">
-        <v>-20.1048472967136</v>
+        <v>-11.46550738046959</v>
       </c>
       <c r="F74">
-        <v>0.868959743391382</v>
+        <v>3.793696413273264</v>
       </c>
       <c r="G74">
-        <v>-12.74439617075306</v>
+        <v>-8.57037035278853</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.452262776553964</v>
       </c>
       <c r="E75">
-        <v>-19.26961158002263</v>
+        <v>-11.31830511148369</v>
       </c>
       <c r="F75">
-        <v>0.4686984129304805</v>
+        <v>3.535606951787439</v>
       </c>
       <c r="G75">
-        <v>-12.05395212932576</v>
+        <v>-8.542704292356502</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.565704802764952</v>
       </c>
       <c r="E76">
-        <v>-19.49529293020249</v>
+        <v>-11.57051302239523</v>
       </c>
       <c r="F76">
-        <v>1.740806494429028</v>
+        <v>3.47967392801561</v>
       </c>
       <c r="G76">
-        <v>-12.87077578954738</v>
+        <v>-8.344828127562252</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.662578197810582</v>
       </c>
       <c r="E77">
-        <v>-18.58218865438231</v>
+        <v>-12.22253812791404</v>
       </c>
       <c r="F77">
-        <v>0.7567855431738841</v>
+        <v>3.2452608636366</v>
       </c>
       <c r="G77">
-        <v>-12.63466135409939</v>
+        <v>-8.637542200373284</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.739543965445538</v>
       </c>
       <c r="E78">
-        <v>-19.20832679371346</v>
+        <v>-12.52111664326728</v>
       </c>
       <c r="F78">
-        <v>1.479208068624944</v>
+        <v>3.487848257546436</v>
       </c>
       <c r="G78">
-        <v>-12.2654929313099</v>
+        <v>-8.369285582891802</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.795714958361412</v>
       </c>
       <c r="E79">
-        <v>-18.71571439847555</v>
+        <v>-13.14846752030529</v>
       </c>
       <c r="F79">
-        <v>1.208391570362507</v>
+        <v>3.365891038301876</v>
       </c>
       <c r="G79">
-        <v>-11.30550909143459</v>
+        <v>-7.699394628258044</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.823125300355274</v>
       </c>
       <c r="E80">
-        <v>-20.50213103241273</v>
+        <v>-13.09340424456071</v>
       </c>
       <c r="F80">
-        <v>1.215926400258372</v>
+        <v>3.30975754961857</v>
       </c>
       <c r="G80">
-        <v>-12.76304863548427</v>
+        <v>-7.815588427030132</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.819401297268987</v>
       </c>
       <c r="E81">
-        <v>-20.64133836959833</v>
+        <v>-14.02101568753851</v>
       </c>
       <c r="F81">
-        <v>0.7365766920151875</v>
+        <v>3.523835850993657</v>
       </c>
       <c r="G81">
-        <v>-11.67600507784866</v>
+        <v>-7.371069999224228</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.773875786149146</v>
       </c>
       <c r="E82">
-        <v>-22.69690801665234</v>
+        <v>-14.38443413809498</v>
       </c>
       <c r="F82">
-        <v>1.245454384698563</v>
+        <v>3.511469982404666</v>
       </c>
       <c r="G82">
-        <v>-11.51604214600656</v>
+        <v>-7.909699242678288</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.683601025598527</v>
       </c>
       <c r="E83">
-        <v>-22.32125835874425</v>
+        <v>-15.75157578236807</v>
       </c>
       <c r="F83">
-        <v>0.7959143058125216</v>
+        <v>3.150049971093631</v>
       </c>
       <c r="G83">
-        <v>-12.28443779943531</v>
+        <v>-7.617737064309498</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.538419341719278</v>
       </c>
       <c r="E84">
-        <v>-23.53014188548475</v>
+        <v>-16.69913509933903</v>
       </c>
       <c r="F84">
-        <v>0.7396714726320464</v>
+        <v>3.36996991939326</v>
       </c>
       <c r="G84">
-        <v>-11.28437250322494</v>
+        <v>-7.691145980722422</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.336217428772684</v>
       </c>
       <c r="E85">
-        <v>-23.34346749606767</v>
+        <v>-17.19977980527916</v>
       </c>
       <c r="F85">
-        <v>1.22712261407461</v>
+        <v>3.304676343969798</v>
       </c>
       <c r="G85">
-        <v>-11.78701002174591</v>
+        <v>-7.629754321662393</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.070655065674162</v>
       </c>
       <c r="E86">
-        <v>-24.59289467176114</v>
+        <v>-18.27507113654521</v>
       </c>
       <c r="F86">
-        <v>0.3352128045411598</v>
+        <v>2.947529051722402</v>
       </c>
       <c r="G86">
-        <v>-10.9834345849519</v>
+        <v>-7.212574305842332</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.74272820048823</v>
       </c>
       <c r="E87">
-        <v>-26.30614002857749</v>
+        <v>-19.0420612847466</v>
       </c>
       <c r="F87">
-        <v>1.084916782036019</v>
+        <v>3.308662447912069</v>
       </c>
       <c r="G87">
-        <v>-10.80376575293607</v>
+        <v>-7.236201544391907</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.354186912143874</v>
       </c>
       <c r="E88">
-        <v>-27.00605166067157</v>
+        <v>-20.15336926462157</v>
       </c>
       <c r="F88">
-        <v>1.056929560965035</v>
+        <v>3.249682688832745</v>
       </c>
       <c r="G88">
-        <v>-11.44787691010488</v>
+        <v>-7.301660743524891</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.911799340976682</v>
       </c>
       <c r="E89">
-        <v>-28.82062291417976</v>
+        <v>-22.35249466111829</v>
       </c>
       <c r="F89">
-        <v>1.058417308820462</v>
+        <v>2.985017646903497</v>
       </c>
       <c r="G89">
-        <v>-10.21562243293926</v>
+        <v>-6.826907282609304</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.427424155304384</v>
       </c>
       <c r="E90">
-        <v>-29.02460788839872</v>
+        <v>-23.56362922839684</v>
       </c>
       <c r="F90">
-        <v>0.9834218943754122</v>
+        <v>2.975019252351707</v>
       </c>
       <c r="G90">
-        <v>-10.91955619166884</v>
+        <v>-6.951426745882452</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.912035214790658</v>
       </c>
       <c r="E91">
-        <v>-31.63660402269663</v>
+        <v>-25.37160933553252</v>
       </c>
       <c r="F91">
-        <v>0.8310751885917494</v>
+        <v>2.910143174099255</v>
       </c>
       <c r="G91">
-        <v>-10.93531464602079</v>
+        <v>-6.749694511327129</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.38476748248616</v>
       </c>
       <c r="E92">
-        <v>-32.65006026715298</v>
+        <v>-27.26583918225092</v>
       </c>
       <c r="F92">
-        <v>0.01178172232250962</v>
+        <v>2.847167370668825</v>
       </c>
       <c r="G92">
-        <v>-10.54911242014659</v>
+        <v>-6.757740826156939</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.856097186029766</v>
       </c>
       <c r="E93">
-        <v>-33.67421726058775</v>
+        <v>-28.52280443649896</v>
       </c>
       <c r="F93">
-        <v>0.5525590153202913</v>
+        <v>2.632363419448886</v>
       </c>
       <c r="G93">
-        <v>-11.18342545286495</v>
+        <v>-7.096826944395325</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-5.346482157040722</v>
       </c>
       <c r="E94">
-        <v>-34.4086836109044</v>
+        <v>-30.66797961788615</v>
       </c>
       <c r="F94">
-        <v>0.9873085942293474</v>
+        <v>2.615506142801916</v>
       </c>
       <c r="G94">
-        <v>-10.77823789232417</v>
+        <v>-6.581353700092144</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.861308905079373</v>
       </c>
       <c r="E95">
-        <v>-38.74676060161805</v>
+        <v>-32.83915805537809</v>
       </c>
       <c r="F95">
-        <v>1.285389977187527</v>
+        <v>2.349142947696929</v>
       </c>
       <c r="G95">
-        <v>-10.73291536622244</v>
+        <v>-6.702275557318738</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.411916614352985</v>
       </c>
       <c r="E96">
-        <v>-39.65475850411435</v>
+        <v>-35.12131652928643</v>
       </c>
       <c r="F96">
-        <v>0.187779145823501</v>
+        <v>1.814776390029413</v>
       </c>
       <c r="G96">
-        <v>-11.48563741449845</v>
+        <v>-6.995665812978867</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.9941828980563</v>
       </c>
       <c r="E97">
-        <v>-42.03671864615833</v>
+        <v>-37.71223303950519</v>
       </c>
       <c r="F97">
-        <v>-0.03090404994374891</v>
+        <v>2.193333666169564</v>
       </c>
       <c r="G97">
-        <v>-11.00181161612875</v>
+        <v>-6.612105660630867</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.603763887312269</v>
       </c>
       <c r="E98">
-        <v>-42.32464002125207</v>
+        <v>-39.20972114460236</v>
       </c>
       <c r="F98">
-        <v>0.9010258455537509</v>
+        <v>1.738902906137395</v>
       </c>
       <c r="G98">
-        <v>-10.50357972910528</v>
+        <v>-7.387645616633207</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.232369478779567</v>
       </c>
       <c r="E99">
-        <v>-46.57139723965822</v>
+        <v>-41.91495687314267</v>
       </c>
       <c r="F99">
-        <v>-0.304454160635424</v>
+        <v>1.952207512358268</v>
       </c>
       <c r="G99">
-        <v>-11.468847716033</v>
+        <v>-6.91354745260999</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-2.863787437531935</v>
       </c>
       <c r="E100">
-        <v>-46.31388463958204</v>
+        <v>-44.57600450979248</v>
       </c>
       <c r="F100">
-        <v>0.2395446531918449</v>
+        <v>1.670996659925503</v>
       </c>
       <c r="G100">
-        <v>-10.66252969204603</v>
+        <v>-7.323564890644331</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-2.502629820302555</v>
       </c>
       <c r="E101">
-        <v>-48.09258356857486</v>
+        <v>-46.82122016896648</v>
       </c>
       <c r="F101">
-        <v>0.1043915412206887</v>
+        <v>0.8861168890381654</v>
       </c>
       <c r="G101">
-        <v>-11.2720145437029</v>
+        <v>-7.219725135277391</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-2.11978871745949</v>
       </c>
       <c r="E102">
-        <v>-50.5778268081475</v>
+        <v>-48.7552865804098</v>
       </c>
       <c r="F102">
-        <v>-0.111127291067867</v>
+        <v>0.9793761479801394</v>
       </c>
       <c r="G102">
-        <v>-10.9975665454236</v>
+        <v>-7.024376171247339</v>
       </c>
     </row>
   </sheetData>
